--- a/branches/dependabot/github_actions/dev/actions-d025328a43/ValueSet-mii-vs-seltene-nbs-target-analyte.xlsx
+++ b/branches/dependabot/github_actions/dev/actions-d025328a43/ValueSet-mii-vs-seltene-nbs-target-analyte.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T01:49:31+00:00</t>
+    <t>2026-09-14T01:49:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Leitanalyten der Zielkrankheiten des deutschen Neugeborenenscreenings nach G-BA Kinder-Richtlinie § 17 Abs. 1 (20 Zielkrankheiten) und § 23 ff. (Mukoviszidose). Je Zielkrankheit der Analyt, über den sie im Screening erkannt wird.</t>
+    <t>Leitanalyten der Zielkrankheiten des deutschen Neugeborenenscreenings nach G-BA Kinder-Richtlinie § 17 Abs. 1 (20 Zielkrankheiten) und 23 ff. (Mukoviszidose). Je Zielkrankheit der Analyt, über den sie im Screening erkannt wird.</t>
   </si>
   <si>
     <t>Purpose</t>
